--- a/공정모델링/B3_정점정밀화_DOE.xlsx
+++ b/공정모델링/B3_정점정밀화_DOE.xlsx
@@ -35,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +62,11 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -75,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -89,6 +94,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -609,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -722,9 +728,15 @@
       <c r="G5" t="n">
         <v>26</v>
       </c>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
+      <c r="H5" s="5" t="n">
+        <v>0.9854000000000001</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>25.619</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>기준점(운영점) 재확인 — 반복3회 평균 0.985와 대조</t>
@@ -757,9 +769,15 @@
       <c r="G6" t="n">
         <v>26</v>
       </c>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
+      <c r="H6" s="9" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>24.842</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>정점 왼쪽 0.5 — 여기가 더 높으면 정점&lt;60</t>
@@ -792,9 +810,15 @@
       <c r="G7" t="n">
         <v>26</v>
       </c>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
+      <c r="H7" s="9" t="n">
+        <v>0.9078000000000001</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>23.603</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>정점 오른쪽 0.5 — 여기가 더 높으면 정점&gt;60</t>
@@ -809,7 +833,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>○ 선택</t>
+          <t>— 불필요(결과 A)</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -844,7 +868,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>○ 선택</t>
+          <t>— 불필요(결과 A)</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -883,11 +907,85 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>■ 결론 (결과 A)</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>정점 kV*</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>59.89 ≈ 60 (포물선 3점 피팅). 1차 회귀 kv*=59.96과 일치 → 레시피 kV*≈60 확정, 보정 불필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>최대 Q</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>정점에서 0.988. 26µm은 약 1.2% 언더사이즈가 구조적 한계(정점에서도 완벽히 못 맞춤).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>창(window)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>kV60만 게이트(0.97~1.03) 통과. kV59.5=0.956·kV60.5=0.908 둘 다 탈락 → 창이 ±0.5kV보다 좁음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>비대칭</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>+0.5kV(60.5)는 7.8%p 급락, -0.5kV(59.5)는 3.0%p 하락 → 높은 쪽이 2.6배 위험.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>실무 반영</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>트림 폭을 ±0.5→실질 ±0.3kV 이내로 축소. 세팅 오차 불가피 시 약간 낮게(kV↓) 치우치는 게 안전. kV 캘리브레이션 관리가 최대 리스크.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="9">
+    <mergeCell ref="B14:K14"/>
+    <mergeCell ref="B11:K11"/>
+    <mergeCell ref="B17:K17"/>
+    <mergeCell ref="B18:K18"/>
+    <mergeCell ref="B13:K13"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="B15:K15"/>
+    <mergeCell ref="B16:K16"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B11:K11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
